--- a/output/miso_fuel_mix_daily.xlsx
+++ b/output/miso_fuel_mix_daily.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/output/miso_fuel_mix_daily.xlsx
+++ b/output/miso_fuel_mix_daily.xlsx
@@ -52489,37 +52489,37 @@
         <v>46294</v>
       </c>
       <c r="B1367" t="n">
-        <v>10593.26909090909</v>
+        <v>10595.84668989547</v>
       </c>
       <c r="C1367" t="n">
-        <v>24118.92</v>
+        <v>24182.30662020906</v>
       </c>
       <c r="D1367" t="n">
-        <v>23886.11272727273</v>
+        <v>23826.22648083624</v>
       </c>
       <c r="F1367" t="n">
-        <v>11025.12</v>
+        <v>11062.82578397212</v>
       </c>
       <c r="G1367" t="n">
-        <v>6933.545454545455</v>
+        <v>6643.641114982578</v>
       </c>
       <c r="H1367" t="n">
-        <v>-100.3781818181818</v>
+        <v>-104.1707317073171</v>
       </c>
       <c r="I1367" t="n">
-        <v>1171.465454545455</v>
+        <v>1103.655052264808</v>
       </c>
       <c r="J1367" t="n">
-        <v>79092.20727272728</v>
+        <v>78840.51219512196</v>
       </c>
       <c r="K1367" t="n">
-        <v>1464.152727272727</v>
+        <v>1530.18118466899</v>
       </c>
       <c r="L1367" t="n">
-        <v>0.227059859293344</v>
+        <v>0.2245858937995362</v>
       </c>
       <c r="M1367" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
